--- a/public/files/Data_By_Towns_Index/Burlington/Edgewater Park Township.xlsx
+++ b/public/files/Data_By_Towns_Index/Burlington/Edgewater Park Township.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,664 +425,467 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Owner Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Owner Name</t>
+          <t>Property Location</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Property Location</t>
+          <t>Municipality</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Municipality</t>
+          <t>County</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>State</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Longitude</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DARJI, NILESHKUMAR B &amp; BHOGILAL M</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>101 E FRANKLIN AVE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Edgewater Park Township</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>-74.9115374</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.0589302</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ChIJwzuwB2VMwYkRXSeTV-IRP2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DARJI, BHARAT KUMAR &amp; AMRUTABEN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>438 S ARTHUR DR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Edgewater Park Township</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>-74.9016326</v>
+      </c>
+      <c r="G3" t="n">
+        <v>40.0568089</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ChIJNVA1uW1MwYkRNaPUMolLUjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PATEL, CHETAN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>307 N GARDEN BLVD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Edgewater Park Township</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>-74.9001152</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40.0567561</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ChIJf_ArCW1MwYkRlYpLWcdIM1g</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>JOSHI, SHIVAM</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>464 S ARTHUR DR</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Edgewater Park Township</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Joshi</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Edgewater Park Township</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>-74.89790289999999</v>
+      </c>
+      <c r="G5" t="n">
         <v>40.05786639999999</v>
       </c>
-      <c r="G2" t="n">
-        <v>-74.89790289999999</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>KUMAR, VIPAN</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>319 GREEN ST</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Edgewater Park Township</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Kumar</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>40.051206</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-74.91753609999999</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KUMAR, VIPAN</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1010 COOPER ST</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Edgewater Park Township</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Kumar</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>40.0567856</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-74.91190279999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>KUMAR, VIPAN</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>JEFFERSON SQUARE A9</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Edgewater Park Township</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Kumar</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>40.0509948</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-74.90550990000001</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ChIJ6dD-0WxMwYkRZ89qoap7CVM</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BHATT, PRADIP &amp; HANSA</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PATEL, ARPITABEN S, &amp; SAURABHKU D</t>
+          <t>15 CRYSTAL DRIVE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JEFFERSON SQUARE E11</t>
+          <t>Edgewater Park Township</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Edgewater Park Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>40.0509948</v>
+        <v>-74.8992901</v>
       </c>
       <c r="G6" t="n">
-        <v>-74.90550990000001</v>
+        <v>40.0544694</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ChIJDeR2mXJMwYkRmA8tZSw-Uv0</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SHARMA, SIMONA</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PATEL, BRIJESH</t>
+          <t>27 F FLOYD AVE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARBOR GREEN 4G3</t>
+          <t>Edgewater Park Township</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Edgewater Park Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>40.0512706</v>
+        <v>-74.900453</v>
       </c>
       <c r="G7" t="n">
-        <v>-74.9151253</v>
+        <v>40.0525329</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ChIJVx2lqnNMwYkRSwcy3l5MRL8</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PATEL, POONMA D &amp; DHAVAL N &amp; P, J</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PATEL, CHETAN</t>
+          <t>22 F FLOYD AVE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>307 N GARDEN BLVD</t>
+          <t>Edgewater Park Township</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Edgewater Park Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>40.0567561</v>
+        <v>-74.9003539</v>
       </c>
       <c r="G8" t="n">
-        <v>-74.9001152</v>
+        <v>40.052096</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ChIJb5KdB3NMwYkRLSfCj1Th1zM</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PATEL, DAHYABHAI &amp; BHARTIBEN &amp; BIJA</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PATEL, DAHYABHAI &amp; BHARTIBEN &amp; BIJA</t>
+          <t>7 L WENDOWSKI ST</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>7 L WENDOWSKI ST</t>
+          <t>Edgewater Park Township</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Edgewater Park Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>40.0509886</v>
+        <v>-74.90062499999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-74.90064289999999</v>
+        <v>40.051025</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ChIJBZxFnHNMwYkRh51Aped4FIU</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PATEL, JINAY</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PATEL, FALGUNIBEN</t>
+          <t>6 BENFORD LANE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>61 BENFORD LANE</t>
+          <t>Edgewater Park Township</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Edgewater Park Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>40.05118849999999</v>
+        <v>-74.90322479999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-74.90350239999999</v>
+        <v>40.05046309999999</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ChIJ6zmD_3NMwYkR6wXO7IfWxMg</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PATEL, SATISHBHAI &amp; SHEFALI</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PATEL, JINAY</t>
+          <t>5 BENFORD LANE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6 BENFORD LANE</t>
+          <t>Edgewater Park Township</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Edgewater Park Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>40.05046309999999</v>
+        <v>-74.903339</v>
       </c>
       <c r="G11" t="n">
-        <v>-74.90322479999999</v>
+        <v>40.0508854</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ChIJj-ImVnFMwYkRXjDisFRwK2g</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PATEL, RIKET B &amp; RAVAL, PRACHI D</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PATEL, RIKET B &amp; RAVAL, PRACHI D</t>
+          <t>56 BENFORD LANE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>56 BENFORD LANE</t>
+          <t>Edgewater Park Township</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Edgewater Park Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>-74.9035947</v>
+      </c>
+      <c r="G12" t="n">
         <v>40.0513267</v>
       </c>
-      <c r="G12" t="n">
-        <v>-74.9035947</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PATEL, SATISHBHAI &amp; SHEFALI</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>5 BENFORD LANE</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Edgewater Park Township</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>40.0508854</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-74.903339</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PATEL, SAURABHKUMAR D &amp; ARPITABEN S</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>COOPER VALLEY VILLAGE C6</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Edgewater Park Township</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>40.0431785</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-74.9192276</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SHARMA, CHETAN</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ARBOR GREEN 5F2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Edgewater Park Township</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Sharma</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>40.0512706</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-74.9151253</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BHATT, PRADIP &amp; HANSA</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>15 CRYSTAL DRIVE</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Edgewater Park Township</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Bhatt</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>40.0544694</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-74.8992901</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>DARJI, ASHISHKUMAR &amp; HIRAL</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>JEFFERSON SQUARE A16</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Edgewater Park Township</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Darji</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>40.0509948</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-74.90550990000001</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>DARJI, BHARAT KUMAR &amp; AMRUTABEN</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>438 S ARTHUR DR</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Edgewater Park Township</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Darji</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>40.0568089</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-74.9016326</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DARJI, NILESHKUMAR B &amp; BHOGILAL M</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>101 E FRANKLIN AVE</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Edgewater Park Township</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Darji</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>40.0589302</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-74.9115374</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DARJI, PARUL N</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>JEFFERSON SQUARE A2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Edgewater Park Township</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Darji</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>40.0509948</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-74.90550990000001</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>DARJI, RAMESHCHANDRA</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>JEFFERSON SQUARE A5</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Edgewater Park Township</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Darji</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>40.0509948</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-74.90550990000001</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ChIJmZXpWHFMwYkR6eiNO0QjSdE</t>
+        </is>
       </c>
     </row>
   </sheetData>
